--- a/final_outputs/excel_tables/table_vif.xlsx
+++ b/final_outputs/excel_tables/table_vif.xlsx
@@ -452,7 +452,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.105</v>
+        <v>1.091</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -482,7 +482,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.06</v>
+        <v>1.068</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -512,7 +512,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.084</v>
+        <v>1.077</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
